--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28570,6 +28570,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1227" t="n">
+        <v>6260</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>1.80499994754791</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="F1227" t="n">
+        <v>1.88999998569489</v>
+      </c>
+      <c r="G1227" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28593,6 +28593,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1228" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="F1228" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="G1228" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28616,6 +28616,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>1700</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>1.83000004291534</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28480,22 +28480,22 @@
     </row>
     <row r="1223">
       <c r="A1223" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1223" t="n">
-        <v>26201</v>
+        <v>13166</v>
       </c>
       <c r="C1223" t="n">
-        <v>1.83500003814697</v>
+        <v>1.875</v>
       </c>
       <c r="D1223" t="n">
-        <v>1.70000004768372</v>
+        <v>1.82500004768372</v>
       </c>
       <c r="E1223" t="n">
-        <v>1.83500003814697</v>
+        <v>1.82500004768372</v>
       </c>
       <c r="F1223" t="n">
-        <v>1.78999996185303</v>
+        <v>1.875</v>
       </c>
       <c r="G1223" t="s">
         <v>7</v>
@@ -28503,22 +28503,22 @@
     </row>
     <row r="1224">
       <c r="A1224" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1224" t="n">
-        <v>7810</v>
+        <v>26201</v>
       </c>
       <c r="C1224" t="n">
-        <v>1.89999997615814</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="D1224" t="n">
-        <v>1.77499997615814</v>
+        <v>1.70000004768372</v>
       </c>
       <c r="E1224" t="n">
-        <v>1.85000002384186</v>
+        <v>1.83500003814697</v>
       </c>
       <c r="F1224" t="n">
-        <v>1.88999998569489</v>
+        <v>1.78999996185303</v>
       </c>
       <c r="G1224" t="s">
         <v>7</v>
@@ -28526,22 +28526,22 @@
     </row>
     <row r="1225">
       <c r="A1225" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1225" t="n">
-        <v>18370</v>
+        <v>7810</v>
       </c>
       <c r="C1225" t="n">
-        <v>1.90499997138977</v>
+        <v>1.89999997615814</v>
       </c>
       <c r="D1225" t="n">
-        <v>1.75499999523163</v>
+        <v>1.77499997615814</v>
       </c>
       <c r="E1225" t="n">
-        <v>1.90499997138977</v>
+        <v>1.85000002384186</v>
       </c>
       <c r="F1225" t="n">
-        <v>1.77499997615814</v>
+        <v>1.88999998569489</v>
       </c>
       <c r="G1225" t="s">
         <v>7</v>
@@ -28549,22 +28549,22 @@
     </row>
     <row r="1226">
       <c r="A1226" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1226" t="n">
-        <v>1310</v>
+        <v>18370</v>
       </c>
       <c r="C1226" t="n">
-        <v>1.86000001430511</v>
+        <v>1.90499997138977</v>
       </c>
       <c r="D1226" t="n">
-        <v>1.82000005245209</v>
+        <v>1.75499999523163</v>
       </c>
       <c r="E1226" t="n">
-        <v>1.86000001430511</v>
+        <v>1.90499997138977</v>
       </c>
       <c r="F1226" t="n">
-        <v>1.86000001430511</v>
+        <v>1.77499997615814</v>
       </c>
       <c r="G1226" t="s">
         <v>7</v>
@@ -28572,22 +28572,22 @@
     </row>
     <row r="1227">
       <c r="A1227" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1227" t="n">
-        <v>6260</v>
+        <v>1310</v>
       </c>
       <c r="C1227" t="n">
-        <v>1.91999995708466</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="D1227" t="n">
-        <v>1.80499994754791</v>
+        <v>1.82000005245209</v>
       </c>
       <c r="E1227" t="n">
-        <v>1.91999995708466</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="F1227" t="n">
-        <v>1.88999998569489</v>
+        <v>1.86000001430511</v>
       </c>
       <c r="G1227" t="s">
         <v>7</v>
@@ -28595,22 +28595,22 @@
     </row>
     <row r="1228">
       <c r="A1228" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1228" t="n">
-        <v>2550</v>
+        <v>6260</v>
       </c>
       <c r="C1228" t="n">
-        <v>1.88499999046326</v>
+        <v>1.91999995708466</v>
       </c>
       <c r="D1228" t="n">
-        <v>1.82500004768372</v>
+        <v>1.80499994754791</v>
       </c>
       <c r="E1228" t="n">
-        <v>1.82500004768372</v>
+        <v>1.91999995708466</v>
       </c>
       <c r="F1228" t="n">
-        <v>1.88499999046326</v>
+        <v>1.88999998569489</v>
       </c>
       <c r="G1228" t="s">
         <v>7</v>
@@ -28618,24 +28618,70 @@
     </row>
     <row r="1229">
       <c r="A1229" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1229" t="n">
+        <v>2550</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>1.82500004768372</v>
+      </c>
+      <c r="F1229" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="G1229" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="n">
         <v>46281.2916666667</v>
       </c>
-      <c r="B1229" t="n">
+      <c r="B1230" t="n">
         <v>1700</v>
       </c>
-      <c r="C1229" t="n">
+      <c r="C1230" t="n">
         <v>1.83000004291534</v>
       </c>
-      <c r="D1229" t="n">
+      <c r="D1230" t="n">
         <v>1.83000004291534</v>
       </c>
-      <c r="E1229" t="n">
+      <c r="E1230" t="n">
         <v>1.83000004291534</v>
       </c>
-      <c r="F1229" t="n">
+      <c r="F1230" t="n">
         <v>1.83000004291534</v>
       </c>
-      <c r="G1229" t="s">
+      <c r="G1230" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1231" t="n">
+        <v>4015</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>1.82000005245209</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>1.7150000333786</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>1.80999994277954</v>
+      </c>
+      <c r="F1231" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="G1231" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706174850464</v>
+        <v>15.7706155776978</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465505599976</v>
+        <v>14.7465515136719</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438278198242</v>
+        <v>14.2438268661499</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645357131958</v>
+        <v>13.9645376205444</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7224836349487</v>
+        <v>13.722484588623</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G12" t="n">
-        <v>13.1080446243286</v>
+        <v>13.1080436706543</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783422470093</v>
+        <v>13.7783432006836</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245748519897</v>
+        <v>13.4245738983154</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708055496216</v>
+        <v>13.0708065032959</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>13.648006439209</v>
+        <v>13.6480073928833</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G23" t="n">
-        <v>13.648006439209</v>
+        <v>13.6480073928833</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>14.0390148162842</v>
+        <v>14.0390138626099</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459161758423</v>
+        <v>13.9459171295166</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065887451172</v>
+        <v>14.2065877914429</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258407592773</v>
+        <v>15.0258417129517</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G65" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.685245513916</v>
+        <v>13.6852464675903</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3369235992432</v>
+        <v>14.3369245529175</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078556060791</v>
+        <v>15.8078536987305</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919578552246</v>
+        <v>16.2919597625732</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727077484131</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727077484131</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609886169434</v>
+        <v>15.360990524292</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609886169434</v>
+        <v>15.360990524292</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.733377456665</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194425582886</v>
+        <v>15.5194435119629</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.424464225769</v>
+        <v>15.4244651794434</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834138870239</v>
+        <v>11.2834148406982</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.0364713668823</v>
+        <v>11.036470413208</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454233169556</v>
+        <v>11.2454223632812</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063404083252</v>
+        <v>11.6063394546509</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.5493535995483</v>
+        <v>11.549352645874</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984788894653</v>
+        <v>10.9984798431396</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465147018433</v>
+        <v>10.8465137481689</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655099868774</v>
+        <v>10.8655090332031</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.409613609314</v>
+        <v>10.4096145629883</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486974716187</v>
+        <v>10.0486965179443</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436758041382</v>
+        <v>10.1436748504639</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.2006616592407</v>
+        <v>10.200662612915</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -32430,6 +32430,32 @@
         <v>1.78999996185303</v>
       </c>
       <c r="H1233" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1234" t="n">
+        <v>10</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="F1234" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="G1234" t="n">
+        <v>1.86000001430511</v>
+      </c>
+      <c r="H1234" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -447,7 +447,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706155776978</v>
+        <v>15.7706174850464</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465515136719</v>
+        <v>14.7465505599976</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438268661499</v>
+        <v>14.2438278198242</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645376205444</v>
+        <v>13.9645366668701</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G12" t="n">
-        <v>13.1080436706543</v>
+        <v>13.1080446243286</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314771652222</v>
+        <v>13.3314781188965</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708065032959</v>
+        <v>13.0708055496216</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>13.6480073928833</v>
+        <v>13.648006439209</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G23" t="n">
-        <v>13.6480073928833</v>
+        <v>13.648006439209</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459171295166</v>
+        <v>13.9459161758423</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G50" t="n">
-        <v>14.4672594070435</v>
+        <v>14.4672603607178</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444602966309</v>
+        <v>15.0444593429565</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.8210287094116</v>
+        <v>14.8210277557373</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258417129517</v>
+        <v>15.0258407592773</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G65" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3369245529175</v>
+        <v>14.3369235992432</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781532287598</v>
+        <v>16.4781513214111</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540872573853</v>
+        <v>15.4540882110596</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727077484131</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727077484131</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5603561401367</v>
+        <v>14.560357093811</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.733377456665</v>
+        <v>15.7333765029907</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099458694458</v>
+        <v>15.5099449157715</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194435119629</v>
+        <v>15.5194425582886</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4244651794434</v>
+        <v>15.424464225769</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834148406982</v>
+        <v>11.2834138870239</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.036470413208</v>
+        <v>11.0364713668823</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454223632812</v>
+        <v>11.2454233169556</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063394546509</v>
+        <v>11.6063404083252</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.549352645874</v>
+        <v>11.5493535995483</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984798431396</v>
+        <v>10.9984788894653</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465137481689</v>
+        <v>10.8465147018433</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655090332031</v>
+        <v>10.8655099868774</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.4096145629883</v>
+        <v>10.409613609314</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486965179443</v>
+        <v>10.0486974716187</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436748504639</v>
+        <v>10.1436758041382</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.200662612915</v>
+        <v>10.2006616592407</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -32456,6 +32456,32 @@
         <v>1.86000001430511</v>
       </c>
       <c r="H1234" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1235" t="n">
+        <v>9851</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>1.83500003814697</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>1.80499994754791</v>
+      </c>
+      <c r="F1235" t="n">
+        <v>1.80499994754791</v>
+      </c>
+      <c r="G1235" t="n">
+        <v>1.80499994754791</v>
+      </c>
+      <c r="H1235" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5712471008301</v>
+        <v>16.5712490081787</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706165313721</v>
+        <v>15.7706174850464</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465515136719</v>
+        <v>14.7465505599976</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996845245361</v>
+        <v>14.2996854782104</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645366668701</v>
+        <v>13.9645357131958</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.722484588623</v>
+        <v>13.7224836349487</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783432006836</v>
+        <v>13.7783422470093</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G14" t="n">
-        <v>13.4618139266968</v>
+        <v>13.4618129730225</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314771652222</v>
+        <v>13.3314781188965</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G18" t="n">
-        <v>13.4618139266968</v>
+        <v>13.4618129730225</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708065032959</v>
+        <v>13.0708055496216</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4059534072876</v>
+        <v>13.4059543609619</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>13.4059534072876</v>
+        <v>13.4059543609619</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>14.0390138626099</v>
+        <v>14.0390148162842</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459171295166</v>
+        <v>13.9459161758423</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348352432251</v>
+        <v>14.6348342895508</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G47" t="n">
-        <v>14.6720724105835</v>
+        <v>14.6720733642578</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.8210277557373</v>
+        <v>14.8210287094116</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>13.8714399337769</v>
+        <v>13.8714389801025</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6852464675903</v>
+        <v>13.685245513916</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3369245529175</v>
+        <v>14.3369235992432</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078546524048</v>
+        <v>15.8078556060791</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919597625732</v>
+        <v>16.2919578552246</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781532287598</v>
+        <v>16.4781513214111</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G106" t="n">
-        <v>15.0816993713379</v>
+        <v>15.0817003250122</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G115" t="n">
-        <v>15.0816993713379</v>
+        <v>15.0817003250122</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G118" t="n">
-        <v>15.0816993713379</v>
+        <v>15.0817003250122</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>15.0816993713379</v>
+        <v>15.0817003250122</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.733377456665</v>
+        <v>15.7333765029907</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194435119629</v>
+        <v>15.5194425582886</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4244651794434</v>
+        <v>15.424464225769</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834148406982</v>
+        <v>11.2834138870239</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.036470413208</v>
+        <v>11.0364713668823</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454223632812</v>
+        <v>11.2454233169556</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063394546509</v>
+        <v>11.6063404083252</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.549352645874</v>
+        <v>11.5493535995483</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984798431396</v>
+        <v>10.9984788894653</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465137481689</v>
+        <v>10.8465147018433</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655090332031</v>
+        <v>10.8655099868774</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.4096145629883</v>
+        <v>10.409613609314</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486965179443</v>
+        <v>10.0486974716187</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436748504639</v>
+        <v>10.1436758041382</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.200662612915</v>
+        <v>10.2006616592407</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -32586,6 +32586,32 @@
         <v>1.82000005245209</v>
       </c>
       <c r="H1239" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1240" t="n">
+        <v>65064</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>2.19000005722046</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>2</v>
+      </c>
+      <c r="F1240" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="G1240" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="H1240" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28954,8 +28954,31 @@
       <c r="E1243" t="n">
         <v>2.07999992370605</v>
       </c>
-      <c r="F1243"/>
+      <c r="F1243" t="n">
+        <v>2.00999999046326</v>
+      </c>
       <c r="G1243" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1244" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>1.93499994277954</v>
+      </c>
+      <c r="F1244"/>
+      <c r="G1244" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28977,7 +28977,9 @@
       <c r="E1244" t="n">
         <v>1.93499994277954</v>
       </c>
-      <c r="F1244"/>
+      <c r="F1244" t="n">
+        <v>2.01999998092651</v>
+      </c>
       <c r="G1244" t="s">
         <v>7</v>
       </c>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -28984,6 +28984,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="F1245" t="n">
+        <v>2.01999998092651</v>
+      </c>
+      <c r="G1245" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1246" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="F1246"/>
+      <c r="G1246" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -29023,8 +29023,31 @@
       <c r="E1246" t="n">
         <v>1.9099999666214</v>
       </c>
-      <c r="F1246"/>
+      <c r="F1246" t="n">
+        <v>2.00999999046326</v>
+      </c>
       <c r="G1246" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1247" t="n">
+        <v>80</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>1.94500005245209</v>
+      </c>
+      <c r="F1247"/>
+      <c r="G1247" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -29053,6 +29053,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1248" t="n">
+        <v>3280</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>1.98500001430511</v>
+      </c>
+      <c r="F1248" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1248" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -32875,6 +32875,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1251" t="n">
+        <v>1550</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>1.89999997615814</v>
+      </c>
+      <c r="F1251" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G1251" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="H1251" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -421,7 +421,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5712490081787</v>
+        <v>16.5712509155273</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465505599976</v>
+        <v>14.7465515136719</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438278198242</v>
+        <v>14.2438268661499</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645357131958</v>
+        <v>13.9645376205444</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7224836349487</v>
+        <v>13.722484588623</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783422470093</v>
+        <v>13.7783432006836</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G14" t="n">
-        <v>13.4618129730225</v>
+        <v>13.4618139266968</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245748519897</v>
+        <v>13.4245738983154</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G18" t="n">
-        <v>13.4618129730225</v>
+        <v>13.4618139266968</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708055496216</v>
+        <v>13.0708065032959</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4059543609619</v>
+        <v>13.4059553146362</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>13.4059543609619</v>
+        <v>13.4059553146362</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>14.0390148162842</v>
+        <v>14.0390129089355</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065887451172</v>
+        <v>14.2065877914429</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G50" t="n">
-        <v>14.4672594070435</v>
+        <v>14.4672603607178</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.8210287094116</v>
+        <v>14.8210277557373</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582668304443</v>
+        <v>14.8582677841187</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258407592773</v>
+        <v>15.0258417129517</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.685245513916</v>
+        <v>13.6852464675903</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078556060791</v>
+        <v>15.8078536987305</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919578552246</v>
+        <v>16.2919597625732</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540872573853</v>
+        <v>15.4540882110596</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>15.6402797698975</v>
+        <v>15.6402807235718</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G103" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G105" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5603561401367</v>
+        <v>14.560357093811</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.733377456665</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099458694458</v>
+        <v>15.5099449157715</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -32898,6 +32898,32 @@
         <v>1.97000002861023</v>
       </c>
       <c r="H1251" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1252" t="n">
+        <v>3200</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>1.98000001907349</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>1.94000005722046</v>
+      </c>
+      <c r="F1252" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="G1252" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="H1252" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706174850464</v>
+        <v>15.7706165313721</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996854782104</v>
+        <v>14.2996845245361</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.722484588623</v>
+        <v>13.7224836349487</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783432006836</v>
+        <v>13.7783422470093</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245738983154</v>
+        <v>13.4245748519897</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459161758423</v>
+        <v>13.9459171295166</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348342895508</v>
+        <v>14.6348352432251</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065877914429</v>
+        <v>14.2065887451172</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444593429565</v>
+        <v>15.0444602966309</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582668304443</v>
+        <v>14.8582677841187</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837896347046</v>
+        <v>14.7837886810303</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687162399292</v>
+        <v>13.3687152862549</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6852464675903</v>
+        <v>13.685245513916</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078536987305</v>
+        <v>15.8078565597534</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919597625732</v>
+        <v>16.2919578552246</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540882110596</v>
+        <v>15.4540872573853</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.560357093811</v>
+        <v>14.5603561401367</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.7333755493164</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099449157715</v>
+        <v>15.5099458694458</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194425582886</v>
+        <v>15.5194435119629</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.424464225769</v>
+        <v>15.4244651794434</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834138870239</v>
+        <v>11.2834148406982</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.0364713668823</v>
+        <v>11.036470413208</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454233169556</v>
+        <v>11.2454223632812</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063404083252</v>
+        <v>11.6063394546509</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.5493535995483</v>
+        <v>11.549352645874</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984788894653</v>
+        <v>10.9984798431396</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465147018433</v>
+        <v>10.8465137481689</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655099868774</v>
+        <v>10.8655090332031</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.409613609314</v>
+        <v>10.4096145629883</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486974716187</v>
+        <v>10.0486965179443</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436758041382</v>
+        <v>10.1436748504639</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.2006616592407</v>
+        <v>10.200662612915</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>
@@ -36712,6 +36712,35 @@
         <v>10</v>
       </c>
       <c r="I1253" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1254" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>1.97500002384186</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="F1254" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="G1254" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="H1254" t="n">
+        <v>2538</v>
+      </c>
+      <c r="I1254" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706165313721</v>
+        <v>15.7706155776978</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -514,7 +514,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465505599976</v>
+        <v>14.7465515136719</v>
       </c>
       <c r="H5" t="n">
         <v>15552</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996845245361</v>
+        <v>14.2996854782104</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -601,7 +601,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438278198242</v>
+        <v>14.2438268661499</v>
       </c>
       <c r="H8" t="n">
         <v>11664</v>
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645366668701</v>
+        <v>13.9645376205444</v>
       </c>
       <c r="H9" t="n">
         <v>3024</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7224836349487</v>
+        <v>13.722484588623</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -717,7 +717,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G12" t="n">
-        <v>13.1080446243286</v>
+        <v>13.1080436706543</v>
       </c>
       <c r="H12" t="n">
         <v>2448</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783422470093</v>
+        <v>13.7783432006836</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245748519897</v>
+        <v>13.4245738983154</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -920,7 +920,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708055496216</v>
+        <v>13.0708065032959</v>
       </c>
       <c r="H19" t="n">
         <v>3888</v>
@@ -1007,7 +1007,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>13.648006439209</v>
+        <v>13.6480073928833</v>
       </c>
       <c r="H22" t="n">
         <v>1296</v>
@@ -1036,7 +1036,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G23" t="n">
-        <v>13.648006439209</v>
+        <v>13.6480073928833</v>
       </c>
       <c r="H23" t="n">
         <v>16128</v>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H29" t="n">
         <v>13248</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1297,7 +1297,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H32" t="n">
         <v>5616</v>
@@ -1326,7 +1326,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H33" t="n">
         <v>864</v>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H35" t="n">
         <v>4032</v>
@@ -1413,7 +1413,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H36" t="n">
         <v>1152</v>
@@ -1442,7 +1442,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H37" t="n">
         <v>288</v>
@@ -1471,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348352432251</v>
+        <v>14.6348342895508</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065887451172</v>
+        <v>14.2065877914429</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1761,7 +1761,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H48" t="n">
         <v>720</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1819,7 +1819,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G50" t="n">
-        <v>14.4672603607178</v>
+        <v>14.4672594070435</v>
       </c>
       <c r="H50" t="n">
         <v>24192</v>
@@ -1848,7 +1848,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H51" t="n">
         <v>5904</v>
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.8210277557373</v>
+        <v>14.8210287094116</v>
       </c>
       <c r="H55" t="n">
         <v>2160</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582677841187</v>
+        <v>14.8582668304443</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2022,7 +2022,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H57" t="n">
         <v>1728</v>
@@ -2080,7 +2080,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258407592773</v>
+        <v>15.0258417129517</v>
       </c>
       <c r="H59" t="n">
         <v>4464</v>
@@ -2138,7 +2138,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H61" t="n">
         <v>1296</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837886810303</v>
+        <v>14.7837896347046</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2196,7 +2196,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H63" t="n">
         <v>1152</v>
@@ -2225,7 +2225,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H64" t="n">
         <v>720</v>
@@ -2254,7 +2254,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G65" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H65" t="n">
         <v>8352</v>
@@ -2283,7 +2283,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H66" t="n">
         <v>432</v>
@@ -2312,7 +2312,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H67" t="n">
         <v>3888</v>
@@ -2370,7 +2370,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H69" t="n">
         <v>11232</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687152862549</v>
+        <v>13.3687162399292</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.685245513916</v>
+        <v>13.6852464675903</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2776,7 +2776,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3369235992432</v>
+        <v>14.3369245529175</v>
       </c>
       <c r="H83" t="n">
         <v>1296</v>
@@ -2892,7 +2892,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H87" t="n">
         <v>3600</v>
@@ -2921,7 +2921,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078565597534</v>
+        <v>15.8078536987305</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919578552246</v>
+        <v>16.2919597625732</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3472,7 +3472,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H107" t="n">
         <v>432</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727077484131</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727077484131</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609886169434</v>
+        <v>15.360990524292</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609886169434</v>
+        <v>15.360990524292</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H120" t="n">
         <v>144</v>
@@ -3878,7 +3878,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>14.7093114852905</v>
+        <v>14.7093124389648</v>
       </c>
       <c r="H122" t="n">
         <v>432</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333755493164</v>
+        <v>15.733377456665</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -36741,6 +36741,35 @@
         <v>2538</v>
       </c>
       <c r="I1254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1255" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>1.91999995708466</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>1.85000002384186</v>
+      </c>
+      <c r="F1255" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="G1255" t="n">
+        <v>1.9099999666214</v>
+      </c>
+      <c r="H1255" t="n">
+        <v>9836</v>
+      </c>
+      <c r="I1255" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706155776978</v>
+        <v>15.7706174850464</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -514,7 +514,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465515136719</v>
+        <v>14.7465505599976</v>
       </c>
       <c r="H5" t="n">
         <v>15552</v>
@@ -601,7 +601,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438268661499</v>
+        <v>14.2438278198242</v>
       </c>
       <c r="H8" t="n">
         <v>11664</v>
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645376205444</v>
+        <v>13.9645366668701</v>
       </c>
       <c r="H9" t="n">
         <v>3024</v>
@@ -717,7 +717,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G12" t="n">
-        <v>13.1080436706543</v>
+        <v>13.1080446243286</v>
       </c>
       <c r="H12" t="n">
         <v>2448</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314771652222</v>
+        <v>13.3314781188965</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -920,7 +920,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708065032959</v>
+        <v>13.0708055496216</v>
       </c>
       <c r="H19" t="n">
         <v>3888</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1007,7 +1007,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>13.6480073928833</v>
+        <v>13.648006439209</v>
       </c>
       <c r="H22" t="n">
         <v>1296</v>
@@ -1036,7 +1036,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G23" t="n">
-        <v>13.6480073928833</v>
+        <v>13.648006439209</v>
       </c>
       <c r="H23" t="n">
         <v>16128</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459171295166</v>
+        <v>13.9459161758423</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H29" t="n">
         <v>13248</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1297,7 +1297,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H32" t="n">
         <v>5616</v>
@@ -1326,7 +1326,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G33" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H33" t="n">
         <v>864</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H35" t="n">
         <v>4032</v>
@@ -1413,7 +1413,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H36" t="n">
         <v>1152</v>
@@ -1442,7 +1442,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H37" t="n">
         <v>288</v>
@@ -1471,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H48" t="n">
         <v>720</v>
@@ -1819,7 +1819,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G50" t="n">
-        <v>14.4672594070435</v>
+        <v>14.4672603607178</v>
       </c>
       <c r="H50" t="n">
         <v>24192</v>
@@ -1848,7 +1848,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H51" t="n">
         <v>5904</v>
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444602966309</v>
+        <v>15.0444593429565</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1964,7 +1964,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.8210287094116</v>
+        <v>14.8210277557373</v>
       </c>
       <c r="H55" t="n">
         <v>2160</v>
@@ -2022,7 +2022,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955049514771</v>
+        <v>14.8955059051514</v>
       </c>
       <c r="H57" t="n">
         <v>1728</v>
@@ -2080,7 +2080,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258417129517</v>
+        <v>15.0258407592773</v>
       </c>
       <c r="H59" t="n">
         <v>4464</v>
@@ -2138,7 +2138,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G61" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H61" t="n">
         <v>1296</v>
@@ -2196,7 +2196,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G63" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H63" t="n">
         <v>1152</v>
@@ -2225,7 +2225,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G64" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H64" t="n">
         <v>720</v>
@@ -2254,7 +2254,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G65" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H65" t="n">
         <v>8352</v>
@@ -2283,7 +2283,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G66" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H66" t="n">
         <v>432</v>
@@ -2312,7 +2312,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G67" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H67" t="n">
         <v>3888</v>
@@ -2370,7 +2370,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G69" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H69" t="n">
         <v>11232</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G83" t="n">
-        <v>14.3369245529175</v>
+        <v>14.3369235992432</v>
       </c>
       <c r="H83" t="n">
         <v>1296</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2892,7 +2892,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G87" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H87" t="n">
         <v>3600</v>
@@ -2921,7 +2921,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H88" t="n">
         <v>3600</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886026382446</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781532287598</v>
+        <v>16.4781513214111</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540872573853</v>
+        <v>15.4540882110596</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3472,7 +3472,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G107" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H107" t="n">
         <v>432</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727077484131</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727077484131</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.360990524292</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H120" t="n">
         <v>144</v>
@@ -3878,7 +3878,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G121" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>14.7093124389648</v>
+        <v>14.7093114852905</v>
       </c>
       <c r="H122" t="n">
         <v>432</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5603561401367</v>
+        <v>14.560357093811</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.733377456665</v>
+        <v>15.7333765029907</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099458694458</v>
+        <v>15.5099449157715</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194435119629</v>
+        <v>15.5194425582886</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4244651794434</v>
+        <v>15.424464225769</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834148406982</v>
+        <v>11.2834138870239</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.036470413208</v>
+        <v>11.0364713668823</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454223632812</v>
+        <v>11.2454233169556</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063394546509</v>
+        <v>11.6063404083252</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.549352645874</v>
+        <v>11.5493535995483</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984798431396</v>
+        <v>10.9984788894653</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465137481689</v>
+        <v>10.8465147018433</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655090332031</v>
+        <v>10.8655099868774</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.4096145629883</v>
+        <v>10.409613609314</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486965179443</v>
+        <v>10.0486974716187</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436748504639</v>
+        <v>10.1436758041382</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.200662612915</v>
+        <v>10.2006616592407</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>
@@ -36770,6 +36770,35 @@
         <v>9836</v>
       </c>
       <c r="I1255" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1256" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>1.88499999046326</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>1.73000001907349</v>
+      </c>
+      <c r="F1256" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="G1256" t="n">
+        <v>1.74000000953674</v>
+      </c>
+      <c r="H1256" t="n">
+        <v>13510</v>
+      </c>
+      <c r="I1256" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -36802,6 +36802,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1257">
+      <c r="A1257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1257" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>1.77999997138977</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>1.67999994754791</v>
+      </c>
+      <c r="F1257" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="G1257" t="n">
+        <v>1.74500000476837</v>
+      </c>
+      <c r="H1257" t="n">
+        <v>9286</v>
+      </c>
+      <c r="I1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706174850464</v>
+        <v>15.7706165313721</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996854782104</v>
+        <v>14.2996845245361</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.722484588623</v>
+        <v>13.7224836349487</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783432006836</v>
+        <v>13.7783422470093</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245738983154</v>
+        <v>13.4245748519897</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459161758423</v>
+        <v>13.9459171295166</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348342895508</v>
+        <v>14.6348352432251</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065877914429</v>
+        <v>14.2065887451172</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444593429565</v>
+        <v>15.0444602966309</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582668304443</v>
+        <v>14.8582677841187</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837896347046</v>
+        <v>14.7837886810303</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687162399292</v>
+        <v>13.3687152862549</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6852464675903</v>
+        <v>13.685245513916</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078536987305</v>
+        <v>15.8078565597534</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919597625732</v>
+        <v>16.2919578552246</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540882110596</v>
+        <v>15.4540872573853</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.560357093811</v>
+        <v>14.5603561401367</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.7333755493164</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099449157715</v>
+        <v>15.5099458694458</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194425582886</v>
+        <v>15.5194435119629</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.424464225769</v>
+        <v>15.4244651794434</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834138870239</v>
+        <v>11.2834148406982</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.0364713668823</v>
+        <v>11.036470413208</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454233169556</v>
+        <v>11.2454223632812</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063404083252</v>
+        <v>11.6063394546509</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.5493535995483</v>
+        <v>11.549352645874</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984788894653</v>
+        <v>10.9984798431396</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465147018433</v>
+        <v>10.8465137481689</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655099868774</v>
+        <v>10.8655090332031</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.409613609314</v>
+        <v>10.4096145629883</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486974716187</v>
+        <v>10.0486965179443</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436758041382</v>
+        <v>10.1436748504639</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.2006616592407</v>
+        <v>10.200662612915</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>
@@ -36828,6 +36828,35 @@
         <v>9286</v>
       </c>
       <c r="I1257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1258" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>1.75499999523163</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>1.68499994277954</v>
+      </c>
+      <c r="F1258" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G1258" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H1258" t="n">
+        <v>290</v>
+      </c>
+      <c r="I1258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706165313721</v>
+        <v>15.7706174850464</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996845245361</v>
+        <v>14.2996854782104</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7224836349487</v>
+        <v>13.722484588623</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783422470093</v>
+        <v>13.7783432006836</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245748519897</v>
+        <v>13.4245738983154</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314771652222</v>
+        <v>13.3314781188965</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459171295166</v>
+        <v>13.9459161758423</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348352432251</v>
+        <v>14.6348342895508</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065887451172</v>
+        <v>14.2065877914429</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444602966309</v>
+        <v>15.0444593429565</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582677841187</v>
+        <v>14.8582668304443</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837886810303</v>
+        <v>14.7837896347046</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687152862549</v>
+        <v>13.3687162399292</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.685245513916</v>
+        <v>13.6852464675903</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078565597534</v>
+        <v>15.8078536987305</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919578552246</v>
+        <v>16.2919597625732</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781532287598</v>
+        <v>16.4781513214111</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540872573853</v>
+        <v>15.4540882110596</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5603561401367</v>
+        <v>14.560357093811</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333755493164</v>
+        <v>15.7333765029907</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099458694458</v>
+        <v>15.5099449157715</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194435119629</v>
+        <v>15.5194425582886</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4244651794434</v>
+        <v>15.424464225769</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834148406982</v>
+        <v>11.2834138870239</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.036470413208</v>
+        <v>11.0364713668823</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454223632812</v>
+        <v>11.2454233169556</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063394546509</v>
+        <v>11.6063404083252</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.549352645874</v>
+        <v>11.5493535995483</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984798431396</v>
+        <v>10.9984788894653</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465137481689</v>
+        <v>10.8465147018433</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655090332031</v>
+        <v>10.8655099868774</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.4096145629883</v>
+        <v>10.409613609314</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486965179443</v>
+        <v>10.0486974716187</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436748504639</v>
+        <v>10.1436758041382</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.200662612915</v>
+        <v>10.2006616592407</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>
@@ -36857,6 +36857,35 @@
         <v>290</v>
       </c>
       <c r="I1258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1259" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F1259" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G1259" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H1259" t="n">
+        <v>260</v>
+      </c>
+      <c r="I1259" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706174850464</v>
+        <v>15.7706165313721</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996854782104</v>
+        <v>14.2996845245361</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.722484588623</v>
+        <v>13.7224836349487</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783432006836</v>
+        <v>13.7783422470093</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245738983154</v>
+        <v>13.4245748519897</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459161758423</v>
+        <v>13.9459171295166</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348342895508</v>
+        <v>14.6348352432251</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065877914429</v>
+        <v>14.2065887451172</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114017486572</v>
+        <v>14.4114007949829</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576343536377</v>
+        <v>14.0576333999634</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651691436768</v>
+        <v>14.7651700973511</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444593429565</v>
+        <v>15.0444602966309</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582668304443</v>
+        <v>14.8582677841187</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837896347046</v>
+        <v>14.7837886810303</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687162399292</v>
+        <v>13.3687152862549</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6852464675903</v>
+        <v>13.685245513916</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886035919189</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078536987305</v>
+        <v>15.8078565597534</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919597625732</v>
+        <v>16.2919578552246</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540882110596</v>
+        <v>15.4540872573853</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609895706177</v>
+        <v>15.3609886169434</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.560357093811</v>
+        <v>14.5603561401367</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.7333755493164</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189374923706</v>
+        <v>15.1189384460449</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099449157715</v>
+        <v>15.5099458694458</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.671407699585</v>
+        <v>15.6714086532593</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194425582886</v>
+        <v>15.5194435119629</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.424464225769</v>
+        <v>15.4244651794434</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535037994385</v>
+        <v>15.2535028457642</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065603256226</v>
+        <v>15.0065612792969</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.4746828079224</v>
+        <v>14.474681854248</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266469955444</v>
+        <v>14.6266479492188</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.7718439102173</v>
+        <v>13.771842956543</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471708297729</v>
+        <v>12.3471698760986</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834138870239</v>
+        <v>11.2834148406982</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.0364713668823</v>
+        <v>11.036470413208</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454233169556</v>
+        <v>11.2454223632812</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063404083252</v>
+        <v>11.6063394546509</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.5493535995483</v>
+        <v>11.549352645874</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823225021362</v>
+        <v>11.6823234558105</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984788894653</v>
+        <v>10.9984798431396</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465147018433</v>
+        <v>10.8465137481689</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655099868774</v>
+        <v>10.8655090332031</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.409613609314</v>
+        <v>10.4096145629883</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486974716187</v>
+        <v>10.0486965179443</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436758041382</v>
+        <v>10.1436748504639</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.2006616592407</v>
+        <v>10.200662612915</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.63756275177</v>
+        <v>10.6375617980957</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.447606086731</v>
+        <v>10.4476051330566</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -456,7 +456,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7706165313721</v>
+        <v>15.7706174850464</v>
       </c>
       <c r="H3" t="n">
         <v>63792</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -572,7 +572,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2996845245361</v>
+        <v>14.2996854782104</v>
       </c>
       <c r="H7" t="n">
         <v>5184</v>
@@ -659,7 +659,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7224836349487</v>
+        <v>13.722484588623</v>
       </c>
       <c r="H10" t="n">
         <v>1584</v>
@@ -746,7 +746,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7783422470093</v>
+        <v>13.7783432006836</v>
       </c>
       <c r="H13" t="n">
         <v>2448</v>
@@ -804,7 +804,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4245748519897</v>
+        <v>13.4245738983154</v>
       </c>
       <c r="H15" t="n">
         <v>144</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314771652222</v>
+        <v>13.3314781188965</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335674285889</v>
+        <v>13.0335664749146</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1152,7 +1152,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G27" t="n">
-        <v>13.9459171295166</v>
+        <v>13.9459161758423</v>
       </c>
       <c r="H27" t="n">
         <v>1440</v>
@@ -1239,7 +1239,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G30" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H30" t="n">
         <v>2880</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1355,7 +1355,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G34" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H34" t="n">
         <v>2736</v>
@@ -1500,7 +1500,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G39" t="n">
-        <v>14.6348352432251</v>
+        <v>14.6348342895508</v>
       </c>
       <c r="H39" t="n">
         <v>288</v>
@@ -1529,7 +1529,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G40" t="n">
-        <v>14.2065887451172</v>
+        <v>14.2065877914429</v>
       </c>
       <c r="H40" t="n">
         <v>1440</v>
@@ -1558,7 +1558,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H41" t="n">
         <v>288</v>
@@ -1587,7 +1587,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G42" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G43" t="n">
-        <v>14.4114007949829</v>
+        <v>14.4114017486572</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H44" t="n">
         <v>3888</v>
@@ -1674,7 +1674,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>14.0576333999634</v>
+        <v>14.0576343536377</v>
       </c>
       <c r="H45" t="n">
         <v>1440</v>
@@ -1790,7 +1790,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G49" t="n">
-        <v>14.7651700973511</v>
+        <v>14.7651691436768</v>
       </c>
       <c r="H49" t="n">
         <v>5616</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444602966309</v>
+        <v>15.0444593429565</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582677841187</v>
+        <v>14.8582668304443</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2167,7 +2167,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G62" t="n">
-        <v>14.7837886810303</v>
+        <v>14.7837896347046</v>
       </c>
       <c r="H62" t="n">
         <v>1296</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.523118019104</v>
+        <v>14.5231189727783</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900594711304</v>
+        <v>13.8900585174561</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3687152862549</v>
+        <v>13.3687162399292</v>
       </c>
       <c r="H80" t="n">
         <v>3600</v>
@@ -2718,7 +2718,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G81" t="n">
-        <v>13.685245513916</v>
+        <v>13.6852464675903</v>
       </c>
       <c r="H81" t="n">
         <v>576</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162147521973</v>
+        <v>14.6162137985229</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886035919189</v>
+        <v>14.9886016845703</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3008,7 +3008,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G91" t="n">
-        <v>15.8078565597534</v>
+        <v>15.8078536987305</v>
       </c>
       <c r="H91" t="n">
         <v>14832</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153923034668</v>
+        <v>16.5153903961182</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3124,7 +3124,7 @@
         <v>17.5</v>
       </c>
       <c r="G95" t="n">
-        <v>16.2919578552246</v>
+        <v>16.2919597625732</v>
       </c>
       <c r="H95" t="n">
         <v>6624</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781532287598</v>
+        <v>16.4781513214111</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3182,7 +3182,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G97" t="n">
-        <v>15.4540872573853</v>
+        <v>15.4540882110596</v>
       </c>
       <c r="H97" t="n">
         <v>1872</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727067947388</v>
+        <v>15.4727058410645</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>16.5</v>
       </c>
       <c r="G116" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H116" t="n">
         <v>144</v>
@@ -3762,7 +3762,7 @@
         <v>16.5</v>
       </c>
       <c r="G117" t="n">
-        <v>15.3609886169434</v>
+        <v>15.3609895706177</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G123" t="n">
-        <v>14.5603561401367</v>
+        <v>14.560357093811</v>
       </c>
       <c r="H123" t="n">
         <v>864</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333755493164</v>
+        <v>15.7333765029907</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
@@ -4168,7 +4168,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G131" t="n">
-        <v>15.1189384460449</v>
+        <v>15.1189374923706</v>
       </c>
       <c r="H131" t="n">
         <v>576</v>
@@ -4197,7 +4197,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G132" t="n">
-        <v>15.5099458694458</v>
+        <v>15.5099449157715</v>
       </c>
       <c r="H132" t="n">
         <v>432</v>
@@ -4284,7 +4284,7 @@
         <v>16.5</v>
       </c>
       <c r="G135" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H135" t="n">
         <v>1008</v>
@@ -4313,7 +4313,7 @@
         <v>16.5</v>
       </c>
       <c r="G136" t="n">
-        <v>15.6714086532593</v>
+        <v>15.671407699585</v>
       </c>
       <c r="H136" t="n">
         <v>144</v>
@@ -4342,7 +4342,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G137" t="n">
-        <v>15.5194435119629</v>
+        <v>15.5194425582886</v>
       </c>
       <c r="H137" t="n">
         <v>1008</v>
@@ -4371,7 +4371,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.4244651794434</v>
+        <v>15.424464225769</v>
       </c>
       <c r="H138" t="n">
         <v>2448</v>
@@ -4458,7 +4458,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H141" t="n">
         <v>2160</v>
@@ -4487,7 +4487,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G142" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G143" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G144" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G145" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G146" t="n">
-        <v>15.2535028457642</v>
+        <v>15.2535037994385</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G165" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H165" t="n">
         <v>288</v>
@@ -5183,7 +5183,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G166" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G167" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H167" t="n">
         <v>144</v>
@@ -5241,7 +5241,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G168" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>15.0065612792969</v>
+        <v>15.0065603256226</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H170" t="n">
         <v>144</v>
@@ -5328,7 +5328,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H171" t="n">
         <v>144</v>
@@ -5763,7 +5763,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G186" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H186" t="n">
         <v>288</v>
@@ -5792,7 +5792,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G187" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G188" t="n">
-        <v>14.474681854248</v>
+        <v>14.4746828079224</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G193" t="n">
-        <v>14.6266479492188</v>
+        <v>14.6266469955444</v>
       </c>
       <c r="H193" t="n">
         <v>576</v>
@@ -6575,7 +6575,7 @@
         <v>14.5</v>
       </c>
       <c r="G214" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H214" t="n">
         <v>576</v>
@@ -6604,7 +6604,7 @@
         <v>14.5</v>
       </c>
       <c r="G215" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>14.5</v>
       </c>
       <c r="G216" t="n">
-        <v>13.771842956543</v>
+        <v>13.7718439102173</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="G226" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H226" t="n">
         <v>288</v>
@@ -6952,7 +6952,7 @@
         <v>13</v>
       </c>
       <c r="G227" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>13</v>
       </c>
       <c r="G228" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>13</v>
       </c>
       <c r="G229" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="G230" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>13</v>
       </c>
       <c r="G231" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>13</v>
       </c>
       <c r="G232" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>13</v>
       </c>
       <c r="G233" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>13</v>
       </c>
       <c r="G234" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>13</v>
       </c>
       <c r="G235" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>13</v>
       </c>
       <c r="G236" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H236" t="n">
         <v>144</v>
@@ -7329,7 +7329,7 @@
         <v>13</v>
       </c>
       <c r="G240" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H240" t="n">
         <v>288</v>
@@ -7358,7 +7358,7 @@
         <v>13</v>
       </c>
       <c r="G241" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>13</v>
       </c>
       <c r="G242" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>13</v>
       </c>
       <c r="G243" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>13</v>
       </c>
       <c r="G244" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>13</v>
       </c>
       <c r="G245" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="G246" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="G288" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H288" t="n">
         <v>400</v>
@@ -8750,7 +8750,7 @@
         <v>13</v>
       </c>
       <c r="G289" t="n">
-        <v>12.3471698760986</v>
+        <v>12.3471708297729</v>
       </c>
       <c r="H289" t="n">
         <v>288</v>
@@ -9098,7 +9098,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G301" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H301" t="n">
         <v>2935</v>
@@ -9243,7 +9243,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G306" t="n">
-        <v>11.2834148406982</v>
+        <v>11.2834138870239</v>
       </c>
       <c r="H306" t="n">
         <v>721</v>
@@ -9272,7 +9272,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>11.036470413208</v>
+        <v>11.0364713668823</v>
       </c>
       <c r="H307" t="n">
         <v>3214</v>
@@ -9301,7 +9301,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G308" t="n">
-        <v>11.2454223632812</v>
+        <v>11.2454233169556</v>
       </c>
       <c r="H308" t="n">
         <v>1306</v>
@@ -9330,7 +9330,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G309" t="n">
-        <v>11.6063394546509</v>
+        <v>11.6063404083252</v>
       </c>
       <c r="H309" t="n">
         <v>2512</v>
@@ -9388,7 +9388,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H311" t="n">
         <v>364</v>
@@ -9417,7 +9417,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G312" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H312" t="n">
         <v>5696</v>
@@ -9446,7 +9446,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G320" t="n">
-        <v>11.549352645874</v>
+        <v>11.5493535995483</v>
       </c>
       <c r="H320" t="n">
         <v>500</v>
@@ -9852,7 +9852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>11.6823234558105</v>
+        <v>11.6823225021362</v>
       </c>
       <c r="H327" t="n">
         <v>8308</v>
@@ -9939,7 +9939,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G330" t="n">
-        <v>10.9984798431396</v>
+        <v>10.9984788894653</v>
       </c>
       <c r="H330" t="n">
         <v>1594</v>
@@ -10026,7 +10026,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G333" t="n">
-        <v>10.8465137481689</v>
+        <v>10.8465147018433</v>
       </c>
       <c r="H333" t="n">
         <v>344</v>
@@ -10055,7 +10055,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G334" t="n">
-        <v>10.8655090332031</v>
+        <v>10.8655099868774</v>
       </c>
       <c r="H334" t="n">
         <v>735</v>
@@ -10200,7 +10200,7 @@
         <v>11</v>
       </c>
       <c r="G339" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H339" t="n">
         <v>1188</v>
@@ -10229,7 +10229,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G340" t="n">
-        <v>10.4096145629883</v>
+        <v>10.409613609314</v>
       </c>
       <c r="H340" t="n">
         <v>1176</v>
@@ -10403,7 +10403,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>10.0486965179443</v>
+        <v>10.0486974716187</v>
       </c>
       <c r="H346" t="n">
         <v>201</v>
@@ -10577,7 +10577,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G352" t="n">
-        <v>10.1436748504639</v>
+        <v>10.1436758041382</v>
       </c>
       <c r="H352" t="n">
         <v>636</v>
@@ -10606,7 +10606,7 @@
         <v>11</v>
       </c>
       <c r="G353" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H353" t="n">
         <v>900</v>
@@ -10635,7 +10635,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G354" t="n">
-        <v>10.200662612915</v>
+        <v>10.2006616592407</v>
       </c>
       <c r="H354" t="n">
         <v>851</v>
@@ -10809,7 +10809,7 @@
         <v>11</v>
       </c>
       <c r="G360" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H360" t="n">
         <v>4252</v>
@@ -10838,7 +10838,7 @@
         <v>11</v>
       </c>
       <c r="G361" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H361" t="n">
         <v>1436</v>
@@ -10867,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="G362" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H362" t="n">
         <v>450</v>
@@ -11157,7 +11157,7 @@
         <v>11</v>
       </c>
       <c r="G372" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H372" t="n">
         <v>9850</v>
@@ -11186,7 +11186,7 @@
         <v>11</v>
       </c>
       <c r="G373" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H373" t="n">
         <v>8459</v>
@@ -11215,7 +11215,7 @@
         <v>11</v>
       </c>
       <c r="G374" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -11244,7 +11244,7 @@
         <v>11</v>
       </c>
       <c r="G375" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -11273,7 +11273,7 @@
         <v>11</v>
       </c>
       <c r="G376" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H376" t="n">
         <v>2147</v>
@@ -11331,7 +11331,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H378" t="n">
         <v>90</v>
@@ -11360,7 +11360,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>10.6375617980957</v>
+        <v>10.63756275177</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>11</v>
       </c>
       <c r="G381" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H381" t="n">
         <v>10499</v>
@@ -11447,7 +11447,7 @@
         <v>11</v>
       </c>
       <c r="G382" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -11476,7 +11476,7 @@
         <v>11</v>
       </c>
       <c r="G383" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H383" t="n">
         <v>4864</v>
@@ -11505,7 +11505,7 @@
         <v>11</v>
       </c>
       <c r="G384" t="n">
-        <v>10.4476051330566</v>
+        <v>10.447606086731</v>
       </c>
       <c r="H384" t="n">
         <v>400</v>
@@ -36886,6 +36886,64 @@
         <v>260</v>
       </c>
       <c r="I1259" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1260" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F1260" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="G1260" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="H1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1261" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>1.77499997615814</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>1.75999999046326</v>
+      </c>
+      <c r="F1261" t="n">
+        <v>1.77499997615814</v>
+      </c>
+      <c r="G1261" t="n">
+        <v>1.77499997615814</v>
+      </c>
+      <c r="H1261" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I1261" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CFL.MI.xlsx
+++ b/data/CFL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G2" t="n">
-        <v>16.5712490081787</v>
+        <v>16.5712509155273</v>
       </c>
       <c r="H2" t="n">
         <v>83808</v>
@@ -485,7 +485,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H4" t="n">
         <v>21888</v>
@@ -514,7 +514,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7465505599976</v>
+        <v>14.7465515136719</v>
       </c>
       <c r="H5" t="n">
         <v>15552</v>
@@ -601,7 +601,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G8" t="n">
-        <v>14.2438278198242</v>
+        <v>14.2438268661499</v>
       </c>
       <c r="H8" t="n">
         <v>11664</v>
@@ -630,7 +630,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9645366668701</v>
+        <v>13.9645376205444</v>
       </c>
       <c r="H9" t="n">
         <v>3024</v>
@@ -775,7 +775,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G14" t="n">
-        <v>13.4618129730225</v>
+        <v>13.4618139266968</v>
       </c>
       <c r="H14" t="n">
         <v>10656</v>
@@ -862,7 +862,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G17" t="n">
-        <v>13.3314781188965</v>
+        <v>13.3314771652222</v>
       </c>
       <c r="H17" t="n">
         <v>3744</v>
@@ -891,7 +891,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G18" t="n">
-        <v>13.4618129730225</v>
+        <v>13.4618139266968</v>
       </c>
       <c r="H18" t="n">
         <v>144</v>
@@ -920,7 +920,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0708055496216</v>
+        <v>13.0708065032959</v>
       </c>
       <c r="H19" t="n">
         <v>3888</v>
@@ -949,7 +949,7 @@
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H20" t="n">
         <v>3024</v>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="G21" t="n">
-        <v>13.0335664749146</v>
+        <v>13.0335674285889</v>
       </c>
       <c r="H21" t="n">
         <v>4320</v>
@@ -1065,7 +1065,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G24" t="n">
-        <v>13.4059543609619</v>
+        <v>13.4059553146362</v>
       </c>
       <c r="H24" t="n">
         <v>14976</v>
@@ -1094,7 +1094,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G25" t="n">
-        <v>13.4059543609619</v>
+        <v>13.4059553146362</v>
       </c>
       <c r="H25" t="n">
         <v>1296</v>
@@ -1123,7 +1123,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G26" t="n">
-        <v>14.0390138626099</v>
+        <v>14.0390129089355</v>
       </c>
       <c r="H26" t="n">
         <v>7776</v>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H29" t="n">
         <v>13248</v>
@@ -1268,7 +1268,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G31" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H31" t="n">
         <v>1008</v>
@@ -1297,7 +1297,7 @@
         <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H32" t="n">
         <v>5616</v>
@@ -1384,7 +1384,7 @@
         <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H35" t="n">
         <v>4032</v>
@@ -1442,7 +1442,7 @@
         <v>16</v>
       </c>
       <c r="G37" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H37" t="n">
         <v>288</v>
@@ -1471,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="G38" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>16</v>
       </c>
       <c r="G51" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H51" t="n">
         <v>5904</v>
@@ -1877,7 +1877,7 @@
         <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H53" t="n">
         <v>288</v>
@@ -1935,7 +1935,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G54" t="n">
-        <v>15.0444593429565</v>
+        <v>15.0444602966309</v>
       </c>
       <c r="H54" t="n">
         <v>576</v>
@@ -1993,7 +1993,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G56" t="n">
-        <v>14.8582668304443</v>
+        <v>14.8582677841187</v>
       </c>
       <c r="H56" t="n">
         <v>1872</v>
@@ -2022,7 +2022,7 @@
         <v>16</v>
       </c>
       <c r="G57" t="n">
-        <v>14.8955059051514</v>
+        <v>14.8955049514771</v>
       </c>
       <c r="H57" t="n">
         <v>1728</v>
@@ -2080,7 +2080,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G59" t="n">
-        <v>15.0258407592773</v>
+        <v>15.0258417129517</v>
       </c>
       <c r="H59" t="n">
         <v>4464</v>
@@ -2399,7 +2399,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G70" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H70" t="n">
         <v>4752</v>
@@ -2428,7 +2428,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G71" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H71" t="n">
         <v>144</v>
@@ -2457,7 +2457,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G72" t="n">
-        <v>14.5231189727783</v>
+        <v>14.523118019104</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G73" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H73" t="n">
         <v>1152</v>
@@ -2515,7 +2515,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G74" t="n">
-        <v>13.8900585174561</v>
+        <v>13.8900594711304</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H84" t="n">
         <v>1728</v>
@@ -2834,7 +2834,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G85" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H85" t="n">
         <v>1296</v>
@@ -2863,7 +2863,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G86" t="n">
-        <v>14.6162137985229</v>
+        <v>14.6162147521973</v>
       </c>
       <c r="H86" t="n">
         <v>432</v>
@@ -2979,7 +2979,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G90" t="n">
-        <v>14.9886016845703</v>
+        <v>14.9886026382446</v>
       </c>
       <c r="H90" t="n">
         <v>1152</v>
@@ -3066,7 +3066,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G93" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H93" t="n">
         <v>5040</v>
@@ -3095,7 +3095,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G94" t="n">
-        <v>16.5153903961182</v>
+        <v>16.5153923034668</v>
       </c>
       <c r="H94" t="n">
         <v>12960</v>
@@ -3153,7 +3153,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G96" t="n">
-        <v>16.4781513214111</v>
+        <v>16.4781532287598</v>
       </c>
       <c r="H96" t="n">
         <v>576</v>
@@ -3211,7 +3211,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>15.6402797698975</v>
+        <v>15.6402807235718</v>
       </c>
       <c r="H98" t="n">
         <v>720</v>
@@ -3240,7 +3240,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G99" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H99" t="n">
         <v>864</v>
@@ -3269,7 +3269,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G103" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G105" t="n">
-        <v>15.2120351791382</v>
+        <v>15.2120342254639</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G111" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H111" t="n">
         <v>144</v>
@@ -3617,7 +3617,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G112" t="n">
-        <v>15.4727058410645</v>
+        <v>15.4727067947388</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>15.7333765029907</v>
+        <v>15.733377456665</v>
       </c>
       <c r="H128" t="n">
         <v>3744</v>
